--- a/project_plan (1).xlsx
+++ b/project_plan (1).xlsx
@@ -628,6 +628,7 @@
     <col min="1" max="1" width="70.140625" customWidth="1"/>
     <col min="2" max="2" width="44.42578125" customWidth="1"/>
     <col min="3" max="3" width="73.7109375" customWidth="1"/>
+    <col min="7" max="7" width="34.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1138,5 +1139,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>